--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F976AF6F-0C4E-734D-8FE0-BAC2DE3DD36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C786BB-8069-B344-9E9C-D715C2B06D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="39940" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9560" yWindow="3200" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="155">
   <si>
     <t>title</t>
   </si>
@@ -532,6 +532,38 @@
       </rPr>
       <t>.png</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劇迷 Gimy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-劇迷.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>073</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國人線上看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-中國人線上看.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://chinaq.biz/cn/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1275,50 +1307,50 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
+        <v>141</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="E24" t="s">
         <v>36</v>
@@ -1326,16 +1358,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -1343,16 +1375,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
@@ -1360,67 +1392,67 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="3" customFormat="1">
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" s="3" customFormat="1">
       <c r="A30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1428,16 +1460,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>99</v>
+        <v>134</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1445,16 +1477,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1462,16 +1494,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1479,16 +1511,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1496,54 +1528,90 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="3" customFormat="1">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="3" customFormat="1">
+      <c r="A38" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D26" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D27" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D28" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D28" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D29" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D30" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D12" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D30" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D32" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D13" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D31" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D32" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D33" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D34" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D35" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D22" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
-    <hyperlink ref="D36" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D33" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D34" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D35" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D36" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D37" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D24" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
+    <hyperlink ref="D38" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{E0C1F7D9-8079-8749-A72A-81C3D00C2203}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{18346E33-FC51-DE4E-95CC-5C3A0306662D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C786BB-8069-B344-9E9C-D715C2B06D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5390340-F926-0441-A86B-95C0A18F4D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9560" yWindow="3200" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="2560" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="159">
   <si>
     <t>title</t>
   </si>
@@ -559,11 +559,69 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-1401-News/XLK-142-中國人線上看.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://chinaq.biz/cn/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉校長開講</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.chunglaungliu.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中國人線上看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>劉校長</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.png</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -938,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1330,10 +1388,10 @@
         <v>152</v>
       </c>
       <c r="C23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>36</v>
@@ -1341,33 +1399,33 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>35</v>
+        <v>141</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -1375,16 +1433,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
@@ -1392,16 +1450,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -1409,16 +1467,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
@@ -1426,50 +1484,50 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>63</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="3" customFormat="1">
-      <c r="A30" s="1" t="s">
+      <c r="E30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="3" customFormat="1">
+      <c r="A31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" t="s">
-        <v>87</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1477,16 +1535,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>134</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1494,16 +1552,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1511,16 +1569,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1528,16 +1586,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
@@ -1545,16 +1603,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>36</v>
@@ -1562,56 +1620,74 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>137</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="3" customFormat="1">
-      <c r="A38" s="5" t="s">
+      <c r="E38" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="3" customFormat="1">
+      <c r="A39" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D28" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D29" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D30" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D29" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D30" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D31" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D12" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D32" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D33" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D13" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D33" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D34" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D35" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D36" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D37" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D24" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
-    <hyperlink ref="D38" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D34" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D35" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D36" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D37" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D38" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
+    <hyperlink ref="D39" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
     <hyperlink ref="D22" r:id="rId14" xr:uid="{E0C1F7D9-8079-8749-A72A-81C3D00C2203}"/>
     <hyperlink ref="D23" r:id="rId15" xr:uid="{18346E33-FC51-DE4E-95CC-5C3A0306662D}"/>
+    <hyperlink ref="D24" r:id="rId16" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5390340-F926-0441-A86B-95C0A18F4D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059519E9-F133-F14F-9393-F17A0348A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="2560" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2960" yWindow="1720" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="182">
   <si>
     <t>title</t>
   </si>
@@ -237,9 +237,6 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/AiCity-923-Deviantart.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/AiCity-923-Dirbbble.png</t>
   </si>
   <si>
     <t>fig/XLK-1401-News/AiCity-923-CGSociety.jpeg</t>
@@ -622,6 +619,102 @@
       </rPr>
       <t>.png</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影貓電影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.mvcat.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-MVCAT.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>076</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vjshi 視頻素材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.vjshi.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-VJshi.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>077</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考拉新媒體導航</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kaolamedia.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-Kaolamedia.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/AiCity-923-Dirbbble.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>書享家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://shuxiangjia.cn/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-書享家.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>極簡簡歷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.polebrief.com/index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-極簡簡歷.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kapwing 影音編輯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kapwing.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-Kapwing.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -996,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1025,16 +1118,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
+        <v>181</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1042,16 +1135,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1059,16 +1152,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+        <v>165</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1076,16 +1169,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -1093,16 +1186,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -1110,16 +1203,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -1127,16 +1220,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -1144,16 +1237,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -1161,16 +1254,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -1178,16 +1271,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -1195,16 +1288,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -1212,16 +1305,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -1229,67 +1322,67 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
+        <v>122</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
+        <v>123</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
+        <v>178</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1297,16 +1390,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
+        <v>174</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1314,16 +1407,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -1331,16 +1424,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -1348,16 +1441,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -1365,271 +1458,271 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>36</v>
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>36</v>
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>36</v>
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
+      </c>
+      <c r="D25" t="s">
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="3" customFormat="1">
+    <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" s="3" customFormat="1">
       <c r="A37" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1637,57 +1730,165 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="D38" t="s">
+        <v>86</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="3" customFormat="1">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="3" customFormat="1">
+      <c r="A45" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="D45" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D29" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D30" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D31" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D33" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
-    <hyperlink ref="D13" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D34" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D35" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D36" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D37" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D38" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D25" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
-    <hyperlink ref="D39" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{E0C1F7D9-8079-8749-A72A-81C3D00C2203}"/>
-    <hyperlink ref="D23" r:id="rId15" xr:uid="{18346E33-FC51-DE4E-95CC-5C3A0306662D}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D35" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D36" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D37" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
+    <hyperlink ref="D39" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
+    <hyperlink ref="D40" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D41" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D42" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D43" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D44" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D31" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
+    <hyperlink ref="D45" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{E0C1F7D9-8079-8749-A72A-81C3D00C2203}"/>
+    <hyperlink ref="D29" r:id="rId15" xr:uid="{18346E33-FC51-DE4E-95CC-5C3A0306662D}"/>
+    <hyperlink ref="D30" r:id="rId16" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D27" r:id="rId17" xr:uid="{8B476CF3-AF5B-1B48-A770-34E70689CE00}"/>
+    <hyperlink ref="D4" r:id="rId18" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
+    <hyperlink ref="D3" r:id="rId19" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
+    <hyperlink ref="D18" r:id="rId20" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
+    <hyperlink ref="D17" r:id="rId21" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
+    <hyperlink ref="D2" r:id="rId22" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059519E9-F133-F14F-9393-F17A0348A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8AF027-F4D3-B142-BDB3-34759DEE5512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="1720" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15640" yWindow="1020" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="166">
   <si>
     <t>title</t>
   </si>
@@ -472,22 +472,6 @@
   </si>
   <si>
     <t>台灣點歌王</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>美國電視頻道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ustvgo.tv/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/AiCity-923-USTVGo.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -532,34 +516,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劇迷 Gimy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-劇迷.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://gimy.app/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中國人線上看</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://chinaq.biz/cn/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>074</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -569,31 +525,6 @@
   </si>
   <si>
     <t>https://www.chunglaungliu.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>fig/XLK-1401-News/XLK-142-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>中國人線上看</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.png</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -619,22 +550,6 @@
       </rPr>
       <t>.png</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>影貓電影</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.mvcat.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-MVCAT.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1089,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1118,16 +1033,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1135,16 +1050,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1152,16 +1067,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1226,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1373,16 +1288,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1390,16 +1305,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1543,16 +1458,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1560,67 +1475,67 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1628,101 +1543,101 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>35</v>
+        <v>83</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" s="3" customFormat="1">
       <c r="A33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="3" customFormat="1">
+    <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>66</v>
+        <v>118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1730,16 +1645,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" t="s">
-        <v>86</v>
+        <v>131</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1747,16 +1662,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1764,131 +1679,59 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>100</v>
+    <row r="41" spans="1:5" s="3" customFormat="1">
+      <c r="A41" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" t="s">
-        <v>107</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B44" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="3" customFormat="1">
-      <c r="A45" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E45" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D35" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D36" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D37" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D31" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D32" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D33" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D39" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D35" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D40" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D41" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D42" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D43" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D44" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D31" r:id="rId12" xr:uid="{7A7CA156-06B3-744C-B311-41FC5CE35278}"/>
-    <hyperlink ref="D45" r:id="rId13" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D28" r:id="rId14" xr:uid="{E0C1F7D9-8079-8749-A72A-81C3D00C2203}"/>
-    <hyperlink ref="D29" r:id="rId15" xr:uid="{18346E33-FC51-DE4E-95CC-5C3A0306662D}"/>
-    <hyperlink ref="D30" r:id="rId16" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
-    <hyperlink ref="D27" r:id="rId17" xr:uid="{8B476CF3-AF5B-1B48-A770-34E70689CE00}"/>
-    <hyperlink ref="D4" r:id="rId18" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
-    <hyperlink ref="D3" r:id="rId19" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
-    <hyperlink ref="D18" r:id="rId20" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
-    <hyperlink ref="D17" r:id="rId21" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
-    <hyperlink ref="D2" r:id="rId22" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
+    <hyperlink ref="D36" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D37" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D38" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D39" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D40" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D41" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D27" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
+    <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
+    <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
+    <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8AF027-F4D3-B142-BDB3-34759DEE5512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750D286F-5E5A-5F4F-92D2-5EF29EA96465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15640" yWindow="1020" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="500" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="170">
   <si>
     <t>title</t>
   </si>
@@ -445,10 +445,6 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-Nasa.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-紀錄片.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -630,6 +626,87 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-Kapwing.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紀錄片500部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>紀錄片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.jpeg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>紀錄片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>部</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.jpeg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/d-7oy3gdhH8yN6vApjThuQ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -693,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -701,6 +778,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1004,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1033,16 +1111,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1050,16 +1128,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1067,16 +1145,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
         <v>146</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1141,7 +1219,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1288,16 +1366,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" t="s">
         <v>159</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C17" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1305,16 +1383,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" t="s">
         <v>155</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1458,16 +1536,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" t="s">
         <v>142</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1583,7 +1661,7 @@
         <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
         <v>86</v>
@@ -1628,16 +1706,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1645,16 +1723,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1662,16 +1740,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1679,35 +1757,52 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="3" customFormat="1">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="3" customFormat="1">
+      <c r="A42" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D42" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1721,17 +1816,18 @@
     <hyperlink ref="D35" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
     <hyperlink ref="D36" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D37" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D38" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D39" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D40" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D41" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D38" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D39" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D40" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D41" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D42" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
     <hyperlink ref="D27" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
+    <hyperlink ref="D37" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750D286F-5E5A-5F4F-92D2-5EF29EA96465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C50CB38-5774-484A-99CB-9DA2A53936AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="500" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17260" yWindow="1120" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="174">
   <si>
     <t>title</t>
   </si>
@@ -707,6 +707,22 @@
   </si>
   <si>
     <t>https://mp.weixin.qq.com/s/d-7oy3gdhH8yN6vApjThuQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://radio.garden/visit/taipei/EJ081eH6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-RadioGarden.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radio Garden</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1082,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1536,16 +1552,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1553,33 +1569,33 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
         <v>36</v>
@@ -1587,16 +1603,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
@@ -1604,16 +1620,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1621,50 +1637,50 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="3" customFormat="1">
+    <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="3" customFormat="1">
+      <c r="A34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" t="s">
-        <v>86</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1672,16 +1688,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
@@ -1689,16 +1705,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>36</v>
@@ -1706,16 +1722,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1723,16 +1739,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1740,16 +1756,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1757,16 +1773,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1774,60 +1790,78 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="3" customFormat="1">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="3" customFormat="1">
+      <c r="A43" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D31" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D32" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D33" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D32" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D33" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D34" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D35" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D36" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D36" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D38" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D39" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D40" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D41" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D42" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D27" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D37" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D39" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D40" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D41" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D42" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D43" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D28" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D37" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D38" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D27" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C50CB38-5774-484A-99CB-9DA2A53936AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE7A574-F256-7044-B593-2818097BCD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17260" yWindow="1120" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9500" yWindow="5060" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="177">
   <si>
     <t>title</t>
   </si>
@@ -723,6 +723,18 @@
   </si>
   <si>
     <t>Radio Garden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/eS-iCMvTGITMq_y55HwXuQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一万本有声书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-一万本有声书.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1098,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1552,16 +1564,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1569,16 +1581,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1586,33 +1598,33 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
@@ -1620,16 +1632,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1637,16 +1649,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -1654,50 +1666,50 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="3" customFormat="1">
+    <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="3" customFormat="1">
+      <c r="A35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>86</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
@@ -1705,16 +1717,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>36</v>
@@ -1722,16 +1734,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1739,16 +1751,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1756,16 +1768,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1773,16 +1785,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1790,16 +1802,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1807,61 +1819,79 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="3" customFormat="1">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="3" customFormat="1">
+      <c r="A44" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D32" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D33" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D34" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D33" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D34" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D35" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D36" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D37" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D37" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D39" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D40" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D41" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D42" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D43" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D28" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D38" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D40" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D41" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D42" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D43" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D44" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D29" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D38" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D27" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D39" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D28" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D27" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE7A574-F256-7044-B593-2818097BCD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB733DF2-A026-384D-8509-43F7D23C55BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9500" yWindow="5060" windowWidth="39880" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27980" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="181">
   <si>
     <t>title</t>
   </si>
@@ -734,7 +734,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-1401-News/XLK-142-一万本有声书.jpg</t>
+    <t>77</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/aOBtIf7LiZSv2705GhYBJg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唐诗三百首微电影合集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>一万本有声书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>唐詩三百首.png</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1110,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1564,16 +1613,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1581,16 +1630,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1598,16 +1647,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1615,33 +1664,33 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1649,16 +1698,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -1666,16 +1715,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
@@ -1683,50 +1732,50 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="3" customFormat="1">
+    <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="3" customFormat="1">
+      <c r="A36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" t="s">
-        <v>86</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>36</v>
@@ -1734,16 +1783,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1751,16 +1800,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1768,16 +1817,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1785,16 +1834,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1802,16 +1851,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1819,16 +1868,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1836,62 +1885,80 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="3" customFormat="1">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="3" customFormat="1">
+      <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D33" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D34" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D35" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D34" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D35" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D36" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D37" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D38" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D38" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D40" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D41" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D42" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D43" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D44" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D29" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D39" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D41" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D42" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D43" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D44" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D45" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D30" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D39" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D28" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D27" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D40" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D29" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D28" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D27" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB733DF2-A026-384D-8509-43F7D23C55BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1500B43-7F60-7A41-916E-A17BCD2FE649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27980" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="183">
   <si>
     <t>title</t>
   </si>
@@ -734,10 +734,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>77</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://mp.weixin.qq.com/s/aOBtIf7LiZSv2705GhYBJg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -784,6 +780,18 @@
       </rPr>
       <t>唐詩三百首.png</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勵志正能量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ananfree.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-勵志正能量.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1159,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1613,16 +1621,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1630,16 +1638,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C28" t="s">
         <v>179</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1647,16 +1655,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1664,16 +1672,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1681,33 +1689,33 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -1715,16 +1723,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
@@ -1732,16 +1740,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -1749,50 +1757,50 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="3" customFormat="1">
+    <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="3" customFormat="1">
+      <c r="A37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" t="s">
-        <v>86</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1800,16 +1808,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D38" t="s">
+        <v>86</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1817,16 +1825,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1834,16 +1842,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1851,16 +1859,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1868,16 +1876,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1885,16 +1893,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1902,63 +1910,81 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="3" customFormat="1">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="3" customFormat="1">
+      <c r="A46" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D34" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D35" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D36" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D35" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D36" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D37" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D38" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D39" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D39" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D41" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D42" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D43" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D44" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D45" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D30" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D40" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D42" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D43" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D44" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D45" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D46" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D31" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D40" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D29" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D28" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D27" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D41" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D30" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D29" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D28" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D27" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1500B43-7F60-7A41-916E-A17BCD2FE649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BEBF26-9B2E-EC42-A5A5-CB1CF4D6536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="186">
   <si>
     <t>title</t>
   </si>
@@ -792,6 +792,18 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-勵志正能量.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>職場攻略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-職場攻略.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.mydesign-cases.com/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1167,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1621,16 +1633,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1638,16 +1650,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1655,16 +1667,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1672,16 +1684,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1689,16 +1701,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1706,33 +1718,33 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
@@ -1740,16 +1752,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -1757,16 +1769,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -1774,50 +1786,50 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="3" customFormat="1">
+    <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="3" customFormat="1">
+      <c r="A38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" t="s">
-        <v>86</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -1825,16 +1837,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1842,16 +1854,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1859,16 +1871,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1876,16 +1888,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1893,16 +1905,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1910,16 +1922,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -1927,64 +1939,82 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="3" customFormat="1">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="3" customFormat="1">
+      <c r="A47" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D35" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D36" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D37" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D36" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D37" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D38" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D39" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D40" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D40" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D42" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D43" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D44" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D45" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D46" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D31" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D41" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D43" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D44" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D45" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D46" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D47" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D32" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D41" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D30" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D29" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D28" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D27" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D42" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D31" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D30" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D29" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D28" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BEBF26-9B2E-EC42-A5A5-CB1CF4D6536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6EF7A2-8B55-8F4F-A8CA-E77D045E6052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="190">
   <si>
     <t>title</t>
   </si>
@@ -804,6 +804,22 @@
   </si>
   <si>
     <t>http://www.mydesign-cases.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50+Fifty Plus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fiftyplus.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-fiftyplus.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1179,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1633,16 +1649,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1650,16 +1666,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1667,16 +1683,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1684,16 +1700,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1701,16 +1717,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1718,16 +1734,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1735,33 +1751,33 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -1769,16 +1785,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -1786,16 +1802,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>40</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1803,50 +1819,50 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>63</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="3" customFormat="1">
-      <c r="A38" s="1" t="s">
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="3" customFormat="1">
+      <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" t="s">
-        <v>86</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -1854,16 +1870,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D40" t="s">
+        <v>86</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1871,16 +1887,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1888,16 +1904,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1905,16 +1921,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1922,16 +1938,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -1939,16 +1955,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
@@ -1956,65 +1972,83 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>135</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>140</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="3" customFormat="1">
-      <c r="A47" s="5" t="s">
+      <c r="E47" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="3" customFormat="1">
+      <c r="A48" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D36" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D37" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D38" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D37" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D38" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D39" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D40" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D41" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D41" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D43" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D44" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D45" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D46" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D47" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D32" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D42" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D44" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D45" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D46" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D47" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D48" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D33" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D42" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D31" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D30" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D29" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D28" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
-    <hyperlink ref="D27" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D43" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D32" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D31" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D30" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D29" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D28" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D27" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6EF7A2-8B55-8F4F-A8CA-E77D045E6052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B9C137-8C27-4148-961B-539220163AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="194">
   <si>
     <t>title</t>
   </si>
@@ -820,6 +820,22 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-fiftyplus.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PressPlay Academy, PPA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.pressplay.cc/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-PPA.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1195,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1649,16 +1665,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1666,16 +1682,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1683,16 +1699,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1700,16 +1716,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1717,16 +1733,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1734,16 +1750,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1751,16 +1767,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1768,33 +1784,33 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -1802,16 +1818,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1819,16 +1835,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -1836,50 +1852,50 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>63</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="3" customFormat="1">
-      <c r="A39" s="1" t="s">
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="3" customFormat="1">
+      <c r="A40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" t="s">
-        <v>86</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>36</v>
@@ -1887,16 +1903,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1904,16 +1920,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1921,16 +1937,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1938,16 +1954,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -1955,16 +1971,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
@@ -1972,16 +1988,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>36</v>
@@ -1989,66 +2005,84 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>135</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>140</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="3" customFormat="1">
-      <c r="A48" s="5" t="s">
+      <c r="E48" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="3" customFormat="1">
+      <c r="A49" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D37" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D38" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D39" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D38" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D39" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D40" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D41" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D42" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D42" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D44" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D45" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D46" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D47" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D48" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D33" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D43" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D45" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D46" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D47" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D48" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D49" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D34" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D43" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D32" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D31" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D30" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D29" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
-    <hyperlink ref="D28" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
+    <hyperlink ref="D44" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D33" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D32" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D31" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D30" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D29" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D28" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
+    <hyperlink ref="D27" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B9C137-8C27-4148-961B-539220163AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FA9451-1376-A442-B1BB-DFB8B7C5ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="198">
   <si>
     <t>title</t>
   </si>
@@ -836,6 +836,22 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-PPA.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>閱讀前哨戰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://readingoutpost.com/podcast/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-Learning.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1211,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1665,16 +1681,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1682,16 +1698,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1699,16 +1715,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B29" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1716,16 +1732,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1733,16 +1749,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1750,16 +1766,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1767,16 +1783,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1784,16 +1800,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1801,33 +1817,33 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1835,16 +1851,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -1852,16 +1868,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
       </c>
       <c r="E38" t="s">
         <v>36</v>
@@ -1869,50 +1885,50 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>63</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="3" customFormat="1">
-      <c r="A40" s="1" t="s">
+      <c r="E40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="3" customFormat="1">
+      <c r="A41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" t="s">
-        <v>132</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>36</v>
@@ -1920,16 +1936,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D42" t="s">
+        <v>86</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>36</v>
@@ -1937,16 +1953,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1954,16 +1970,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -1971,16 +1987,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
@@ -1988,16 +2004,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>36</v>
@@ -2005,16 +2021,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>36</v>
@@ -2022,67 +2038,85 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>135</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="3" customFormat="1">
-      <c r="A49" s="5" t="s">
+      <c r="E49" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="3" customFormat="1">
+      <c r="A50" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D38" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D39" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D40" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D39" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D40" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D41" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D42" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D43" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D43" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D45" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D46" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D47" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D48" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D49" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D34" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D44" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D46" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D47" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D48" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D49" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D50" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D35" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D44" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D33" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D32" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D31" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D30" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
-    <hyperlink ref="D29" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
-    <hyperlink ref="D28" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
-    <hyperlink ref="D27" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
+    <hyperlink ref="D45" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D34" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D33" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D32" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D31" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D29" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
+    <hyperlink ref="D27" r:id="rId27" xr:uid="{59738127-641C-F94C-8B2D-6157209E0572}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FA9451-1376-A442-B1BB-DFB8B7C5ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9B471-6ABF-9147-80B5-7C4D1E842683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="206">
   <si>
     <t>title</t>
   </si>
@@ -852,6 +852,38 @@
   </si>
   <si>
     <t>fig/XLK-1401-News/XLK-142-Learning.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眼底城市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-眼底城市.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://eyesonplace.net/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>084</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>康健</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-康健.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.commonhealth.com.tw/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1681,16 +1713,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1698,16 +1730,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1715,16 +1747,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1732,16 +1764,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1749,16 +1781,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1766,16 +1798,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1783,16 +1815,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1800,16 +1832,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1817,16 +1849,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
@@ -1834,50 +1866,50 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s">
         <v>36</v>
@@ -1885,16 +1917,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>38</v>
       </c>
       <c r="E39" t="s">
         <v>36</v>
@@ -1902,67 +1934,67 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>81</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
       </c>
       <c r="E40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="3" customFormat="1">
+    <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" t="s">
-        <v>86</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="3" customFormat="1">
       <c r="A43" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>36</v>
@@ -1970,16 +2002,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
+        <v>86</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -1987,16 +2019,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>166</v>
+        <v>116</v>
+      </c>
+      <c r="B45" t="s">
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
@@ -2004,16 +2036,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>36</v>
@@ -2021,16 +2053,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B47" t="s">
-        <v>103</v>
+        <v>165</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>36</v>
@@ -2038,16 +2070,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>36</v>
@@ -2055,68 +2087,104 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B51" t="s">
         <v>135</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C51" t="s">
         <v>140</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="3" customFormat="1">
-      <c r="A50" s="5" t="s">
+      <c r="E51" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="3" customFormat="1">
+      <c r="A52" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D52" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D39" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D40" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D41" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D41" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D42" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D43" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D43" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D45" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D44" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D46" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D47" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D48" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D49" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D50" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D35" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D46" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D48" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D49" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D50" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D51" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D52" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D37" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D45" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D34" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D33" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D32" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D31" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
-    <hyperlink ref="D30" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
-    <hyperlink ref="D29" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
-    <hyperlink ref="D27" r:id="rId27" xr:uid="{59738127-641C-F94C-8B2D-6157209E0572}"/>
+    <hyperlink ref="D47" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D36" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D35" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D34" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D33" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D32" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D31" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
+    <hyperlink ref="D30" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{59738127-641C-F94C-8B2D-6157209E0572}"/>
+    <hyperlink ref="D28" r:id="rId28" xr:uid="{28BE47E9-212A-564A-B713-66BCFC03BBD8}"/>
+    <hyperlink ref="D27" r:id="rId29" xr:uid="{237C4A74-8EDE-5449-9E3D-6897CE9A12FB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9B471-6ABF-9147-80B5-7C4D1E842683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397947C8-F741-1844-B2AE-3BD2714C3EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="209">
   <si>
     <t>title</t>
   </si>
@@ -884,6 +884,18 @@
   </si>
   <si>
     <t>https://www.commonhealth.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/fS-9xUqU_VVTuk4ApFnshA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟着书本去旅行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-跟着书本去旅行.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1259,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1715,14 +1727,14 @@
       <c r="A27" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B27" t="s">
-        <v>203</v>
+      <c r="B27" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
@@ -1730,16 +1742,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>36</v>
@@ -1747,16 +1759,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>36</v>
@@ -1764,16 +1776,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>36</v>
@@ -1781,16 +1793,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>36</v>
@@ -1798,16 +1810,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>36</v>
@@ -1815,16 +1827,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -1832,16 +1844,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -1849,16 +1861,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>36</v>
@@ -1866,16 +1878,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>36</v>
@@ -1883,16 +1895,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>36</v>
@@ -1900,33 +1912,33 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
         <v>36</v>
@@ -1934,16 +1946,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
         <v>36</v>
@@ -1951,16 +1963,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
       </c>
       <c r="E41" t="s">
         <v>36</v>
@@ -1968,50 +1980,50 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>63</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="3" customFormat="1">
-      <c r="A43" s="1" t="s">
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="3" customFormat="1">
+      <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" t="s">
-        <v>86</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -2019,16 +2031,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>36</v>
@@ -2036,16 +2048,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>36</v>
@@ -2053,16 +2065,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>166</v>
+        <v>117</v>
+      </c>
+      <c r="B47" t="s">
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>36</v>
@@ -2070,16 +2082,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>36</v>
@@ -2087,16 +2099,16 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>36</v>
@@ -2104,16 +2116,16 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -2121,70 +2133,88 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>135</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>140</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="3" customFormat="1">
-      <c r="A52" s="5" t="s">
+      <c r="E52" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="3" customFormat="1">
+      <c r="A53" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D53" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D41" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
-    <hyperlink ref="D42" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
-    <hyperlink ref="D43" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
+    <hyperlink ref="D42" r:id="rId1" xr:uid="{5D25A6CD-5693-8C46-B530-CBA9FCB0051F}"/>
+    <hyperlink ref="D43" r:id="rId2" xr:uid="{2826745B-3F19-C545-9337-E1F646FAF1FE}"/>
+    <hyperlink ref="D44" r:id="rId3" xr:uid="{7A7EA459-3B5A-2D4C-9748-F6721482A430}"/>
     <hyperlink ref="D15" r:id="rId4" xr:uid="{49DA7E5F-A0BC-ED4B-A142-00829AD03E73}"/>
-    <hyperlink ref="D45" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
+    <hyperlink ref="D46" r:id="rId5" xr:uid="{519390B2-D4B3-9B45-817D-C6A867552723}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{61D8922B-20B5-7A4A-AE2D-7BD6C070E766}"/>
-    <hyperlink ref="D46" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
-    <hyperlink ref="D48" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
-    <hyperlink ref="D49" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
-    <hyperlink ref="D50" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
-    <hyperlink ref="D51" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
-    <hyperlink ref="D52" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
-    <hyperlink ref="D37" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
+    <hyperlink ref="D47" r:id="rId7" xr:uid="{130389F7-B2F6-5B44-9414-FEB0DBDFFD9F}"/>
+    <hyperlink ref="D49" r:id="rId8" xr:uid="{A441C94A-7B17-C243-B4DC-062F879BCC18}"/>
+    <hyperlink ref="D50" r:id="rId9" xr:uid="{BA27F7C3-68E1-2740-8802-6D9785DFDCA3}"/>
+    <hyperlink ref="D51" r:id="rId10" xr:uid="{84A75BB4-C780-E045-9E3F-B4558BA08A59}"/>
+    <hyperlink ref="D52" r:id="rId11" xr:uid="{80718B05-AF44-6345-BFC0-02968B3BE47C}"/>
+    <hyperlink ref="D53" r:id="rId12" xr:uid="{A5261B5E-94E3-3746-A2E2-467077F81302}"/>
+    <hyperlink ref="D38" r:id="rId13" xr:uid="{36C17CFD-2541-0249-A26C-9963FE7E9151}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{73357BBA-D0B4-214C-A7FE-9511B2E182F8}"/>
     <hyperlink ref="D3" r:id="rId15" xr:uid="{657DAB70-5F27-2F4E-BDE5-77F090E99DFB}"/>
     <hyperlink ref="D18" r:id="rId16" xr:uid="{FF99E2B3-9286-5746-AC3E-FBECAB18B196}"/>
     <hyperlink ref="D17" r:id="rId17" xr:uid="{910EFF50-BAAD-9B44-BFB1-5E1A9310F86B}"/>
     <hyperlink ref="D2" r:id="rId18" xr:uid="{99CEEAB5-6157-EE4B-B778-460071820046}"/>
-    <hyperlink ref="D47" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
-    <hyperlink ref="D36" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
-    <hyperlink ref="D35" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
-    <hyperlink ref="D34" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
-    <hyperlink ref="D33" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
-    <hyperlink ref="D32" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
-    <hyperlink ref="D31" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
-    <hyperlink ref="D30" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{59738127-641C-F94C-8B2D-6157209E0572}"/>
-    <hyperlink ref="D28" r:id="rId28" xr:uid="{28BE47E9-212A-564A-B713-66BCFC03BBD8}"/>
-    <hyperlink ref="D27" r:id="rId29" xr:uid="{237C4A74-8EDE-5449-9E3D-6897CE9A12FB}"/>
+    <hyperlink ref="D48" r:id="rId19" xr:uid="{AC71675F-2DF1-064A-BBE9-3413FF836A5F}"/>
+    <hyperlink ref="D37" r:id="rId20" xr:uid="{805EF40B-B3DE-EE49-AA54-CCF3C921E4F2}"/>
+    <hyperlink ref="D36" r:id="rId21" xr:uid="{E797080E-467B-1D45-A665-8AD254395788}"/>
+    <hyperlink ref="D35" r:id="rId22" xr:uid="{193135A5-D1F5-B545-9366-53A3A9EDD151}"/>
+    <hyperlink ref="D34" r:id="rId23" xr:uid="{A0302206-F3EC-3C4E-BC4A-DF87D1D8AD3D}"/>
+    <hyperlink ref="D33" r:id="rId24" xr:uid="{0B2B0B4B-8149-3044-8EBC-5DE584A646ED}"/>
+    <hyperlink ref="D32" r:id="rId25" xr:uid="{42C526F7-8E01-ED40-A4FB-0B8CFB6DA29E}"/>
+    <hyperlink ref="D31" r:id="rId26" xr:uid="{3A5F758E-168D-2747-812B-1259FB46120E}"/>
+    <hyperlink ref="D30" r:id="rId27" xr:uid="{59738127-641C-F94C-8B2D-6157209E0572}"/>
+    <hyperlink ref="D29" r:id="rId28" xr:uid="{28BE47E9-212A-564A-B713-66BCFC03BBD8}"/>
+    <hyperlink ref="D28" r:id="rId29" xr:uid="{237C4A74-8EDE-5449-9E3D-6897CE9A12FB}"/>
+    <hyperlink ref="D27" r:id="rId30" xr:uid="{133A1968-F5B1-BC46-83A6-33873B7FBC57}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1402-Video.xlsx
+++ b/db/A7XLK-1402-Video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397947C8-F741-1844-B2AE-3BD2714C3EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625FDC8A-11EA-6241-A5B1-F966DD8E4B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27780" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
